--- a/Labs/Lab02/Lab2Rubric_CS295N.xlsx
+++ b/Labs/Lab02/Lab2Rubric_CS295N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DataCard/Repos/CS295N-Repos/CS295N-CourseMaterials/Labs/Lab02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1CF8A1-5D66-6A4F-9D29-3B1FC08ACEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD54989-AA7E-3C4C-88CC-EC41F3F34BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="540" windowWidth="14660" windowHeight="15460" activeTab="1" xr2:uid="{BBA0DDDD-2AF9-F84B-99D8-B3B03BF552D8}"/>
+    <workbookView xWindow="1260" yWindow="620" windowWidth="14660" windowHeight="15460" activeTab="1" xr2:uid="{BBA0DDDD-2AF9-F84B-99D8-B3B03BF552D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Rubric" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="37">
   <si>
     <t xml:space="preserve">Total: </t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>Good</t>
+  </si>
+  <si>
+    <t>Good, imssing &lt;/div&gt; in AboutAuthor.cshtml</t>
   </si>
 </sst>
 </file>
@@ -211,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -223,15 +226,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,7 +622,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13">
@@ -657,7 +659,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+      <c r="A18" t="s">
         <v>24</v>
       </c>
       <c r="B18">
@@ -665,7 +667,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19">
@@ -673,7 +675,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" t="s">
         <v>22</v>
       </c>
       <c r="B20">
@@ -814,40 +816,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -869,7 +871,7 @@
       </c>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -886,7 +888,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -962,8 +964,8 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15">
@@ -1038,7 +1040,7 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20">
@@ -1055,7 +1057,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
+      <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21">
@@ -1072,7 +1074,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
       <c r="B22">
@@ -1088,7 +1090,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1099,7 +1101,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>35</v>
@@ -1148,18 +1150,18 @@
       <c r="B29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
@@ -1227,18 +1229,18 @@
       <c r="B52" s="1"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
+      <c r="A54" s="9"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>

--- a/Labs/Lab02/Lab2Rubric_CS295N.xlsx
+++ b/Labs/Lab02/Lab2Rubric_CS295N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DataCard/Repos/CS295N-Repos/CS295N-CourseMaterials/Labs/Lab02/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\CS295N-296N-Repos\CS295N-CourseMaterials\Labs\Lab02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1CF8A1-5D66-6A4F-9D29-3B1FC08ACEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A1C532-8286-468C-8840-EF4BC00FA2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="540" windowWidth="14660" windowHeight="15460" activeTab="1" xr2:uid="{BBA0DDDD-2AF9-F84B-99D8-B3B03BF552D8}"/>
+    <workbookView xWindow="36192" yWindow="4488" windowWidth="16008" windowHeight="12336" activeTab="1" xr2:uid="{BBA0DDDD-2AF9-F84B-99D8-B3B03BF552D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Rubric" sheetId="1" r:id="rId1"/>
@@ -135,9 +135,6 @@
     <t>Yes, SiteMembers</t>
   </si>
   <si>
-    <t>Everything works, even though there are html syntax errors. The Site Members page is interesting--but having a separate controller method for each member is not an approach that is going to work as you add members.</t>
-  </si>
-  <si>
     <t>Very good work!</t>
   </si>
   <si>
@@ -145,6 +142,9 @@
   </si>
   <si>
     <t>Good</t>
+  </si>
+  <si>
+    <t>Everything works, all requirements are met and the code looks good.</t>
   </si>
 </sst>
 </file>
@@ -211,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -223,15 +223,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,19 +546,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB1F9B31-93F6-EA4C-88EB-610E0C385149}">
   <dimension ref="A1:B66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
+    <col min="1" max="1" width="30.69921875" customWidth="1"/>
+    <col min="2" max="2" width="7.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -567,12 +566,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -580,7 +579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -588,17 +587,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -606,7 +605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -614,20 +613,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -635,7 +634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -643,7 +642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -651,36 +650,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>24</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>22</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -688,7 +687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -696,7 +695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -705,92 +704,92 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B55" s="4"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B56" s="4"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B57" s="4"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B58" s="4"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
       <c r="B59" s="4"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B60" s="4"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B61" s="4"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B62" s="4"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B63" s="4"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2"/>
       <c r="B64" s="4"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B65" s="4"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
     </row>
@@ -803,53 +802,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{500450CF-4036-4C7A-B372-CF82A859E7EB}">
   <dimension ref="A1:F72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" customWidth="1"/>
-    <col min="4" max="4" width="1.33203125" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.69921875" customWidth="1"/>
+    <col min="2" max="2" width="7.69921875" customWidth="1"/>
+    <col min="3" max="3" width="6.69921875" customWidth="1"/>
+    <col min="4" max="4" width="1.296875" customWidth="1"/>
+    <col min="5" max="5" width="20.296875" customWidth="1"/>
     <col min="6" max="6" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -863,13 +862,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -886,7 +885,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -903,25 +902,25 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -938,7 +937,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -955,15 +954,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15">
@@ -976,10 +975,10 @@
         <v>30</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -996,7 +995,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1013,7 +1012,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1030,15 +1029,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20">
@@ -1054,8 +1053,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21">
@@ -1071,8 +1070,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
       <c r="B22">
@@ -1088,7 +1087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1099,13 +1098,13 @@
         <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -1122,10 +1121,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -1143,159 +1142,159 @@
       </c>
       <c r="E26" s="6"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E35" s="5"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="E37" s="5"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E38" s="5"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E39" s="5"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E41" s="5"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="E42" s="5"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E44" s="5"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E47" s="5"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E48" s="5"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="E49" s="5"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="9"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="E56" s="1"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="E57" s="5"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E58" s="5"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E63" s="5"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E64" s="5"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E66" s="5"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E67" s="5"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
